--- a/site/leagues/betclic/2026_2027/xlsx/team_packs/team_pack_FCP.xlsx
+++ b/site/leagues/betclic/2026_2027/xlsx/team_packs/team_pack_FCP.xlsx
@@ -13,9 +13,9 @@
     <sheet name="duos_trios" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'overview'!$A$1:$B$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'rotation'!$A$1:$A$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'key_lineups'!$A$1:$A$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'overview'!$A$1:$B$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'rotation'!$A$1:$U$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'key_lineups'!$A$1:$L$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'duos_trios'!$A$1:$J$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -458,7 +458,11 @@
           <t>team_name</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Futebol Clube do Porto</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -468,36 +472,96 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>best_duo</t>
+          <t>primary_scorer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>M. Queiroz | T. Bropleh (11.9 net)</t>
+          <t>T. Bropleh (21 ppg)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>most_used_player</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>T. Bropleh (30.7 mpg)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>best_3pt_pct</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>M. Queiroz (100.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>base_lineup</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>C. Allen Williams | C. Dundao | M. Queiroz | T. Bropleh | X. Williams (16.2 min)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>best_lineup</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>C. Allen Williams | C. Dundao | M. Queiroz | T. Bropleh | X. Williams (-7.4 net)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>best_duo</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>C. Allen Williams | T. Bropleh (8.4 net)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>best_trio</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>C. Dundao | M. Queiroz | T. Bropleh (15.9 net)</t>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>C. Allen Williams | M. Queiroz | T. Bropleh (-13.4 net)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B6"/>
+  <autoFilter ref="A1:B11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -508,28 +572,556 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:U6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="15" customWidth="1" min="19" max="19"/>
+    <col width="23" customWidth="1" min="20" max="20"/>
+    <col width="41" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>team_name</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>player_name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>playing_position</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>games</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>games_started</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>minutes_total</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>mpg</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>ppg</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>rpg</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>apg</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>tov_pg</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>spg</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>bpg</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>fg_pct</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>tp_pct</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>ft_pct</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>efg_pct</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>ts_pct</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>plus_minus_pg</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>on_off_net_diff_per40</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>role_tag</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>sem dados</t>
+          <t>Futebol Clube do Porto</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>T. Bropleh</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>BE</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F2" t="n">
+        <v>61.5</v>
+      </c>
+      <c r="G2" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="H2" t="n">
+        <v>21</v>
+      </c>
+      <c r="I2" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="J2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>61.5%</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>79.2%</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>81.5%</t>
+        </is>
+      </c>
+      <c r="S2" t="n">
+        <v>8</v>
+      </c>
+      <c r="T2" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>high-minutes, primary-scorer, efficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Futebol Clube do Porto</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>C. Allen Williams</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F3" t="n">
+        <v>56.7</v>
+      </c>
+      <c r="G3" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="H3" t="n">
+        <v>13</v>
+      </c>
+      <c r="I3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J3" t="n">
+        <v>5</v>
+      </c>
+      <c r="K3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>38.5%</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>22.2%</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>42.3%</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>46.8%</t>
+        </is>
+      </c>
+      <c r="S3" t="n">
+        <v>9</v>
+      </c>
+      <c r="T3" t="n">
+        <v>-9.699999999999999</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>high-minutes, primary-scorer</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Futebol Clube do Porto</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>C. Dundao</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" t="n">
+        <v>48.4</v>
+      </c>
+      <c r="G4" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="H4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>35.0%</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>12.5%</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>37.5%</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>44.6%</t>
+        </is>
+      </c>
+      <c r="S4" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="T4" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>high-minutes, impact</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Futebol Clube do Porto</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>X. Williams</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" t="n">
+        <v>45.7</v>
+      </c>
+      <c r="G5" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="H5" t="n">
+        <v>12</v>
+      </c>
+      <c r="I5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>47.4%</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>60.5%</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>60.4%</t>
+        </is>
+      </c>
+      <c r="S5" t="n">
+        <v>-2</v>
+      </c>
+      <c r="T5" t="n">
+        <v>-32.1</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>primary-scorer, efficient, shooter</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Futebol Clube do Porto</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>M. Queiroz</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="G6" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="H6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="I6" t="n">
+        <v>7</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>70.8%</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>71.7%</t>
+        </is>
+      </c>
+      <c r="S6" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="T6" t="n">
+        <v>-39.9</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>efficient, shooter</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:A2"/>
+  <autoFilter ref="A1:U6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -540,28 +1132,219 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="19" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="19" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>categoria</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>team_name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>lineup_players</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>games</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>stints</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>minutes</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>pf_per40</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>pa_per40</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>net_per40</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>team_rank_minutes</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>team_rank_net</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>team_rank_defense</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>sem dados</t>
-        </is>
+          <t>Base lineup</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Futebol Clube do Porto</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>C. Allen Williams | C. Dundao | M. Queiroz | T. Bropleh | X. Williams</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F2" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="G2" t="n">
+        <v>98.7</v>
+      </c>
+      <c r="H2" t="n">
+        <v>106.1</v>
+      </c>
+      <c r="I2" t="n">
+        <v>-7.4</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>19</v>
+      </c>
+      <c r="L2" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Best lineup</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Futebol Clube do Porto</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>C. Allen Williams | C. Dundao | M. Queiroz | T. Bropleh | X. Williams</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F3" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="G3" t="n">
+        <v>98.7</v>
+      </c>
+      <c r="H3" t="n">
+        <v>106.1</v>
+      </c>
+      <c r="I3" t="n">
+        <v>-7.4</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>19</v>
+      </c>
+      <c r="L3" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Best defense</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Futebol Clube do Porto</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>C. Allen Williams | C. Dundao | M. Queiroz | T. Bropleh | X. Williams</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="G4" t="n">
+        <v>98.7</v>
+      </c>
+      <c r="H4" t="n">
+        <v>106.1</v>
+      </c>
+      <c r="I4" t="n">
+        <v>-7.4</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>19</v>
+      </c>
+      <c r="L4" t="n">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:A2"/>
+  <autoFilter ref="A1:L4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -657,26 +1440,26 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>M. Queiroz | T. Bropleh</t>
+          <t>C. Allen Williams | T. Bropleh</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="G2" t="n">
-        <v>23.6</v>
+        <v>43</v>
       </c>
       <c r="H2" t="n">
-        <v>116.9</v>
+        <v>104.2</v>
       </c>
       <c r="I2" t="n">
-        <v>105.1</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="J2" t="n">
-        <v>11.9</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="3">
@@ -697,26 +1480,26 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>C. Allen Williams | T. Bropleh</t>
+          <t>C. Dundao | T. Bropleh</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G3" t="n">
-        <v>18</v>
+        <v>42.8</v>
       </c>
       <c r="H3" t="n">
-        <v>119.8</v>
+        <v>103.9</v>
       </c>
       <c r="I3" t="n">
-        <v>90.90000000000001</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>28.8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4">
@@ -737,26 +1520,26 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>C. Allen Williams | T. Bropleh</t>
+          <t>C. Dundao | T. Bropleh</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G4" t="n">
-        <v>18</v>
+        <v>42.8</v>
       </c>
       <c r="H4" t="n">
-        <v>119.8</v>
+        <v>103.9</v>
       </c>
       <c r="I4" t="n">
-        <v>90.90000000000001</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>28.8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5">
@@ -777,26 +1560,26 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>C. Dundao | M. Queiroz | T. Bropleh</t>
+          <t>C. Allen Williams | M. Queiroz | T. Bropleh</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G5" t="n">
-        <v>20.1</v>
+        <v>32.9</v>
       </c>
       <c r="H5" t="n">
-        <v>121.2</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>105.3</v>
+        <v>110.8</v>
       </c>
       <c r="J5" t="n">
-        <v>15.9</v>
+        <v>-13.4</v>
       </c>
     </row>
     <row r="6">
@@ -821,22 +1604,22 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G6" t="n">
-        <v>20.1</v>
+        <v>30.2</v>
       </c>
       <c r="H6" t="n">
-        <v>121.2</v>
+        <v>109.9</v>
       </c>
       <c r="I6" t="n">
-        <v>105.3</v>
+        <v>102</v>
       </c>
       <c r="J6" t="n">
-        <v>15.9</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="7">
@@ -857,26 +1640,26 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>C. Allen Williams | M. Queiroz | T. Bropleh</t>
+          <t>C. Dundao | T. Bropleh | X. Williams</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G7" t="n">
-        <v>15.6</v>
+        <v>30.4</v>
       </c>
       <c r="H7" t="n">
-        <v>110</v>
+        <v>103.8</v>
       </c>
       <c r="I7" t="n">
-        <v>99.8</v>
+        <v>101.2</v>
       </c>
       <c r="J7" t="n">
-        <v>10.2</v>
+        <v>2.6</v>
       </c>
     </row>
   </sheetData>

--- a/site/leagues/betclic/2026_2027/xlsx/team_packs/team_pack_FCP.xlsx
+++ b/site/leagues/betclic/2026_2027/xlsx/team_packs/team_pack_FCP.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'overview'!$A$1:$B$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'rotation'!$A$1:$U$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'rotation'!$A$1:$U$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'key_lineups'!$A$1:$L$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'duos_trios'!$A$1:$J$7</definedName>
   </definedNames>
@@ -472,7 +472,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
     </row>
@@ -484,7 +484,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>T. Bropleh (21 ppg)</t>
+          <t>T. Bropleh (17.7 ppg)</t>
         </is>
       </c>
     </row>
@@ -496,7 +496,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>T. Bropleh (30.7 mpg)</t>
+          <t>T. Bropleh (29.4 mpg)</t>
         </is>
       </c>
     </row>
@@ -520,7 +520,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>C. Allen Williams | C. Dundao | M. Queiroz | T. Bropleh | X. Williams (16.2 min)</t>
+          <t>C. Allen Williams | C. Dundao | M. Queiroz | T. Bropleh | X. Williams (19.9 min)</t>
         </is>
       </c>
     </row>
@@ -532,7 +532,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>C. Allen Williams | C. Dundao | M. Queiroz | T. Bropleh | X. Williams (-7.4 net)</t>
+          <t>C. Allen Williams | C. Dundao | M. Queiroz | T. Bropleh | X. Williams (-12.1 net)</t>
         </is>
       </c>
     </row>
@@ -544,7 +544,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>C. Allen Williams | T. Bropleh (8.4 net)</t>
+          <t>C. Allen Williams | T. Bropleh (9.4 net)</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>C. Allen Williams | M. Queiroz | T. Bropleh (-13.4 net)</t>
+          <t>C. Dundao | T. Bropleh | X. Williams (1.9 net)</t>
         </is>
       </c>
     </row>
@@ -572,7 +572,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U6"/>
+  <dimension ref="A1:U8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -722,65 +722,65 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F2" t="n">
-        <v>61.5</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="G2" t="n">
-        <v>30.7</v>
+        <v>29.4</v>
       </c>
       <c r="H2" t="n">
-        <v>21</v>
+        <v>17.7</v>
       </c>
       <c r="I2" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="J2" t="n">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="K2" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>58.1%</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>61.5%</t>
+          <t>52.9%</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>88.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>79.2%</t>
+          <t>72.6%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>81.5%</t>
+          <t>75.8%</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.2</v>
+        <v>-14.6</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -805,43 +805,43 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
         <v>2</v>
       </c>
       <c r="F3" t="n">
-        <v>56.7</v>
+        <v>86.8</v>
       </c>
       <c r="G3" t="n">
-        <v>28.4</v>
+        <v>28.9</v>
       </c>
       <c r="H3" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I3" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="J3" t="n">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="K3" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>45.0%</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -851,23 +851,23 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>42.3%</t>
+          <t>52.5%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>46.8%</t>
+          <t>56.3%</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>9</v>
+        <v>10.3</v>
       </c>
       <c r="T3" t="n">
-        <v>-9.699999999999999</v>
+        <v>12.9</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>high-minutes, primary-scorer</t>
+          <t>high-minutes, primary-scorer, shooter</t>
         </is>
       </c>
     </row>
@@ -888,69 +888,69 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E4" t="n">
         <v>2</v>
       </c>
       <c r="F4" t="n">
-        <v>48.4</v>
+        <v>68.8</v>
       </c>
       <c r="G4" t="n">
-        <v>24.2</v>
+        <v>22.9</v>
       </c>
       <c r="H4" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="I4" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="J4" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="K4" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>26.9%</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>85.7%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>28.8%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>44.6%</t>
+          <t>42.0%</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>8.5</v>
+        <v>6.7</v>
       </c>
       <c r="T4" t="n">
-        <v>7.3</v>
+        <v>10.8</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>high-minutes, impact</t>
+          <t>impact</t>
         </is>
       </c>
     </row>
@@ -971,69 +971,69 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E5" t="n">
         <v>2</v>
       </c>
       <c r="F5" t="n">
-        <v>45.7</v>
+        <v>66.7</v>
       </c>
       <c r="G5" t="n">
-        <v>22.9</v>
+        <v>22.2</v>
       </c>
       <c r="H5" t="n">
-        <v>12</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>4.5</v>
+        <v>6.7</v>
       </c>
       <c r="J5" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="K5" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="M5" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>47.4%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>60.5%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>60.4%</t>
+          <t>50.4%</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>-2</v>
+        <v>0.3</v>
       </c>
       <c r="T5" t="n">
-        <v>-32.1</v>
+        <v>-14.2</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>primary-scorer, efficient, shooter</t>
+          <t>shooter</t>
         </is>
       </c>
     </row>
@@ -1054,25 +1054,25 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F6" t="n">
-        <v>42.8</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>21.4</v>
+        <v>22</v>
       </c>
       <c r="H6" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="I6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="K6" t="n">
         <v>2</v>
@@ -1081,47 +1081,213 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>73.7%</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>63.6%</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>76.3%</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>75.5%</t>
+        </is>
+      </c>
+      <c r="S6" t="n">
+        <v>-2.7</v>
+      </c>
+      <c r="T6" t="n">
+        <v>-27.4</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>primary-scorer, efficient, shooter</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Futebol Clube do Porto</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>V. Voytso</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>3</v>
+      </c>
+      <c r="E7" t="n">
         <v>1</v>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>66.7%</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="F7" t="n">
+        <v>59.2</v>
+      </c>
+      <c r="G7" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="H7" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>70.0%</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>57.1%</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>90.0%</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>87.3%</t>
+        </is>
+      </c>
+      <c r="S7" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="T7" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>efficient, shooter, impact</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Futebol Clube do Porto</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>J. Woodard</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>BE</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" t="n">
+        <v>55.4</v>
+      </c>
+      <c r="G8" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="H8" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="I8" t="n">
+        <v>3</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>41.2%</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>22.2%</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>66.7%</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>70.8%</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>71.7%</t>
-        </is>
-      </c>
-      <c r="S6" t="n">
-        <v>-4.5</v>
-      </c>
-      <c r="T6" t="n">
-        <v>-39.9</v>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>efficient, shooter</t>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>47.1%</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>57.3%</t>
+        </is>
+      </c>
+      <c r="S8" t="n">
+        <v>2</v>
+      </c>
+      <c r="T8" t="n">
+        <v>-9.300000000000001</v>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>rotation</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:U6"/>
+  <autoFilter ref="A1:U8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1228,31 +1394,31 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F2" t="n">
-        <v>16.2</v>
+        <v>19.9</v>
       </c>
       <c r="G2" t="n">
-        <v>98.7</v>
+        <v>100.8</v>
       </c>
       <c r="H2" t="n">
-        <v>106.1</v>
+        <v>112.8</v>
       </c>
       <c r="I2" t="n">
-        <v>-7.4</v>
+        <v>-12.1</v>
       </c>
       <c r="J2" t="n">
         <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="L2" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3">
@@ -1272,31 +1438,31 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3" t="n">
-        <v>16.2</v>
+        <v>19.9</v>
       </c>
       <c r="G3" t="n">
-        <v>98.7</v>
+        <v>100.8</v>
       </c>
       <c r="H3" t="n">
-        <v>106.1</v>
+        <v>112.8</v>
       </c>
       <c r="I3" t="n">
-        <v>-7.4</v>
+        <v>-12.1</v>
       </c>
       <c r="J3" t="n">
         <v>1</v>
       </c>
       <c r="K3" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="L3" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4">
@@ -1316,31 +1482,31 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F4" t="n">
-        <v>16.2</v>
+        <v>19.9</v>
       </c>
       <c r="G4" t="n">
-        <v>98.7</v>
+        <v>100.8</v>
       </c>
       <c r="H4" t="n">
-        <v>106.1</v>
+        <v>112.8</v>
       </c>
       <c r="I4" t="n">
-        <v>-7.4</v>
+        <v>-12.1</v>
       </c>
       <c r="J4" t="n">
         <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="L4" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -1361,7 +1527,7 @@
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="45" customWidth="1" min="4" max="4"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
@@ -1444,22 +1610,22 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F2" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="G2" t="n">
-        <v>43</v>
+        <v>59.8</v>
       </c>
       <c r="H2" t="n">
-        <v>104.2</v>
+        <v>101.7</v>
       </c>
       <c r="I2" t="n">
-        <v>95.90000000000001</v>
+        <v>92.3</v>
       </c>
       <c r="J2" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="3">
@@ -1484,22 +1650,22 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G3" t="n">
-        <v>42.8</v>
+        <v>54.2</v>
       </c>
       <c r="H3" t="n">
-        <v>103.9</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>88.90000000000001</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>15</v>
+        <v>11.8</v>
       </c>
     </row>
     <row r="4">
@@ -1524,22 +1690,22 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F4" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G4" t="n">
-        <v>42.8</v>
+        <v>54.2</v>
       </c>
       <c r="H4" t="n">
-        <v>103.9</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>88.90000000000001</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="J4" t="n">
-        <v>15</v>
+        <v>11.8</v>
       </c>
     </row>
     <row r="5">
@@ -1560,26 +1726,26 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>C. Allen Williams | M. Queiroz | T. Bropleh</t>
+          <t>C. Dundao | T. Bropleh | X. Williams</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G5" t="n">
-        <v>32.9</v>
+        <v>41.9</v>
       </c>
       <c r="H5" t="n">
         <v>97.40000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>110.8</v>
+        <v>95.5</v>
       </c>
       <c r="J5" t="n">
-        <v>-13.4</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="6">
@@ -1600,26 +1766,26 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>C. Dundao | M. Queiroz | T. Bropleh</t>
+          <t>C. Allen Williams | C. Dundao | T. Bropleh</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F6" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G6" t="n">
-        <v>30.2</v>
+        <v>37</v>
       </c>
       <c r="H6" t="n">
-        <v>109.9</v>
+        <v>96.2</v>
       </c>
       <c r="I6" t="n">
-        <v>102</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>7.9</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="7">
@@ -1640,26 +1806,26 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>C. Dundao | T. Bropleh | X. Williams</t>
+          <t>C. Allen Williams | C. Dundao | T. Bropleh</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F7" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G7" t="n">
-        <v>30.4</v>
+        <v>37</v>
       </c>
       <c r="H7" t="n">
-        <v>103.8</v>
+        <v>96.2</v>
       </c>
       <c r="I7" t="n">
-        <v>101.2</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="J7" t="n">
-        <v>2.6</v>
+        <v>10.8</v>
       </c>
     </row>
   </sheetData>

--- a/site/leagues/betclic/2026_2027/xlsx/team_packs/team_pack_FCP.xlsx
+++ b/site/leagues/betclic/2026_2027/xlsx/team_packs/team_pack_FCP.xlsx
@@ -14,8 +14,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'overview'!$A$1:$B$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'rotation'!$A$1:$U$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'key_lineups'!$A$1:$L$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'rotation'!$A$1:$U$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'key_lineups'!$A$1:$L$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'duos_trios'!$A$1:$J$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -472,7 +472,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
     </row>
@@ -484,7 +484,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>T. Bropleh (17.7 ppg)</t>
+          <t>T. Bropleh (14 ppg)</t>
         </is>
       </c>
     </row>
@@ -496,7 +496,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>T. Bropleh (29.4 mpg)</t>
+          <t>T. Bropleh (27.2 mpg)</t>
         </is>
       </c>
     </row>
@@ -532,7 +532,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>C. Allen Williams | C. Dundao | M. Queiroz | T. Bropleh | X. Williams (-12.1 net)</t>
+          <t>C. Dundao | G. Delgado | J. Woodard | T. Omlid | X. Williams (35.8 net)</t>
         </is>
       </c>
     </row>
@@ -544,7 +544,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>C. Allen Williams | T. Bropleh (9.4 net)</t>
+          <t>C. Allen Williams | T. Bropleh (4.0 net)</t>
         </is>
       </c>
     </row>
@@ -572,7 +572,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U8"/>
+  <dimension ref="A1:U10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -718,47 +718,47 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>G</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E2" t="n">
         <v>3</v>
       </c>
       <c r="F2" t="n">
-        <v>88.09999999999999</v>
+        <v>108.7</v>
       </c>
       <c r="G2" t="n">
-        <v>29.4</v>
+        <v>27.2</v>
       </c>
       <c r="H2" t="n">
-        <v>17.7</v>
+        <v>14</v>
       </c>
       <c r="I2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J2" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="K2" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>58.1%</t>
+          <t>51.4%</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -768,19 +768,19 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>72.6%</t>
+          <t>64.9%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>75.8%</t>
+          <t>68.4%</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>1.5</v>
       </c>
       <c r="T2" t="n">
-        <v>-14.6</v>
+        <v>-23.5</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -805,43 +805,43 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E3" t="n">
         <v>2</v>
       </c>
       <c r="F3" t="n">
-        <v>86.8</v>
+        <v>107.4</v>
       </c>
       <c r="G3" t="n">
-        <v>28.9</v>
+        <v>26.9</v>
       </c>
       <c r="H3" t="n">
-        <v>16</v>
+        <v>13.8</v>
       </c>
       <c r="I3" t="n">
-        <v>3.7</v>
+        <v>3</v>
       </c>
       <c r="J3" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="K3" t="n">
         <v>2</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>45.0%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -851,23 +851,23 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>52.5%</t>
+          <t>51.0%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>56.3%</t>
+          <t>54.3%</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>10.3</v>
+        <v>6.2</v>
       </c>
       <c r="T3" t="n">
-        <v>12.9</v>
+        <v>-4.7</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>high-minutes, primary-scorer, shooter</t>
+          <t>high-minutes, primary-scorer</t>
         </is>
       </c>
     </row>
@@ -888,28 +888,28 @@
         </is>
       </c>
       <c r="D4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E4" t="n">
         <v>3</v>
       </c>
-      <c r="E4" t="n">
-        <v>2</v>
-      </c>
       <c r="F4" t="n">
-        <v>68.8</v>
+        <v>89.3</v>
       </c>
       <c r="G4" t="n">
-        <v>22.9</v>
+        <v>22.3</v>
       </c>
       <c r="H4" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="K4" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="L4" t="n">
         <v>1</v>
@@ -919,34 +919,34 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>26.9%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>85.7%</t>
+          <t>87.5%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>28.8%</t>
+          <t>36.8%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>42.0%</t>
+          <t>47.5%</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>6.7</v>
+        <v>8</v>
       </c>
       <c r="T4" t="n">
-        <v>10.8</v>
+        <v>14.4</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -962,7 +962,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>X. Williams</t>
+          <t>V. Voytso</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -971,69 +971,69 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>66.7</v>
+        <v>85.8</v>
       </c>
       <c r="G5" t="n">
-        <v>22.2</v>
+        <v>21.5</v>
       </c>
       <c r="H5" t="n">
-        <v>9.699999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>6.7</v>
+        <v>2.2</v>
       </c>
       <c r="J5" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="K5" t="n">
-        <v>1.3</v>
+        <v>0.2</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="M5" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>40.7%</t>
+          <t>63.2%</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>85.7%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>86.8%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>50.4%</t>
+          <t>88.3%</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>0.3</v>
+        <v>7.2</v>
       </c>
       <c r="T5" t="n">
-        <v>-14.2</v>
+        <v>6.1</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>shooter</t>
+          <t>efficient, shooter, impact</t>
         </is>
       </c>
     </row>
@@ -1045,78 +1045,78 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>M. Queiroz</t>
+          <t>X. Williams</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E6" t="n">
         <v>3</v>
       </c>
       <c r="F6" t="n">
-        <v>65.90000000000001</v>
+        <v>80</v>
       </c>
       <c r="G6" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H6" t="n">
-        <v>12</v>
+        <v>8.5</v>
       </c>
       <c r="I6" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="J6" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="K6" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="M6" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>73.7%</t>
+          <t>39.4%</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>76.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>75.5%</t>
+          <t>48.9%</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>-2.7</v>
+        <v>2.8</v>
       </c>
       <c r="T6" t="n">
-        <v>-27.4</v>
+        <v>-4.5</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>primary-scorer, efficient, shooter</t>
+          <t>shooter</t>
         </is>
       </c>
     </row>
@@ -1128,78 +1128,78 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>V. Voytso</t>
+          <t>J. Woodard</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>G</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7" t="n">
-        <v>59.2</v>
+        <v>74.8</v>
       </c>
       <c r="G7" t="n">
-        <v>19.7</v>
+        <v>18.7</v>
       </c>
       <c r="H7" t="n">
-        <v>6.3</v>
+        <v>7.8</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>3.5</v>
       </c>
       <c r="J7" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="L7" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="M7" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>47.6%</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>27.3%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>90.0%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>87.3%</t>
+          <t>61.0%</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>9.300000000000001</v>
+        <v>5.8</v>
       </c>
       <c r="T7" t="n">
-        <v>16.3</v>
+        <v>4.8</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>efficient, shooter, impact</t>
+          <t>efficient</t>
         </is>
       </c>
     </row>
@@ -1211,83 +1211,249 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>J. Woodard</t>
+          <t>M. Queiroz</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D8" t="n">
+        <v>4</v>
+      </c>
+      <c r="E8" t="n">
         <v>3</v>
       </c>
-      <c r="E8" t="n">
-        <v>1</v>
-      </c>
       <c r="F8" t="n">
-        <v>55.4</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="G8" t="n">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="H8" t="n">
-        <v>7.7</v>
+        <v>9</v>
       </c>
       <c r="I8" t="n">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="J8" t="n">
         <v>1</v>
       </c>
       <c r="K8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>73.7%</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>63.6%</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>76.3%</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>75.5%</t>
+        </is>
+      </c>
+      <c r="S8" t="n">
+        <v>-2</v>
+      </c>
+      <c r="T8" t="n">
+        <v>-21.7</v>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>efficient, shooter</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Futebol Clube do Porto</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>G. Delgado</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>4</v>
+      </c>
+      <c r="E9" t="n">
         <v>1</v>
       </c>
-      <c r="L8" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="M8" t="n">
+      <c r="F9" t="n">
+        <v>60.8</v>
+      </c>
+      <c r="G9" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="H9" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I9" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M9" t="n">
         <v>0</v>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>41.2%</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>22.2%</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>47.1%</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>57.3%</t>
-        </is>
-      </c>
-      <c r="S8" t="n">
-        <v>2</v>
-      </c>
-      <c r="T8" t="n">
-        <v>-9.300000000000001</v>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>rotation</t>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>48.1%</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>87.5%</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>48.1%</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>54.1%</t>
+        </is>
+      </c>
+      <c r="S9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="T9" t="n">
+        <v>32</v>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>impact</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Futebol Clube do Porto</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>A. Bessa</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>4</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" t="n">
+        <v>56.8</v>
+      </c>
+      <c r="G10" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="H10" t="n">
+        <v>7</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>45.0%</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>46.7%</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>64.3%</t>
+        </is>
+      </c>
+      <c r="S10" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T10" t="n">
+        <v>-6.4</v>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>efficient, shooter</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:U8"/>
+  <autoFilter ref="A1:U10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1298,10 +1464,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
@@ -1415,10 +1581,10 @@
         <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="L2" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3">
@@ -1434,35 +1600,35 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>C. Allen Williams | C. Dundao | M. Queiroz | T. Bropleh | X. Williams</t>
+          <t>C. Dundao | G. Delgado | J. Woodard | T. Omlid | X. Williams</t>
         </is>
       </c>
       <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="G3" t="n">
+        <v>100.9</v>
+      </c>
+      <c r="H3" t="n">
+        <v>65.09999999999999</v>
+      </c>
+      <c r="I3" t="n">
+        <v>35.8</v>
+      </c>
+      <c r="J3" t="n">
         <v>3</v>
       </c>
-      <c r="E3" t="n">
-        <v>3</v>
-      </c>
-      <c r="F3" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="G3" t="n">
-        <v>100.8</v>
-      </c>
-      <c r="H3" t="n">
-        <v>112.8</v>
-      </c>
-      <c r="I3" t="n">
-        <v>-12.1</v>
-      </c>
-      <c r="J3" t="n">
-        <v>1</v>
-      </c>
       <c r="K3" t="n">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="L3" t="n">
-        <v>27</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4">
@@ -1478,39 +1644,83 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>C. Allen Williams | C. Dundao | M. Queiroz | T. Bropleh | X. Williams</t>
+          <t>C. Dundao | G. Delgado | J. Woodard | T. Omlid | X. Williams</t>
         </is>
       </c>
       <c r="D4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="G4" t="n">
+        <v>100.9</v>
+      </c>
+      <c r="H4" t="n">
+        <v>65.09999999999999</v>
+      </c>
+      <c r="I4" t="n">
+        <v>35.8</v>
+      </c>
+      <c r="J4" t="n">
         <v>3</v>
       </c>
-      <c r="E4" t="n">
-        <v>3</v>
-      </c>
-      <c r="F4" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="G4" t="n">
-        <v>100.8</v>
-      </c>
-      <c r="H4" t="n">
-        <v>112.8</v>
-      </c>
-      <c r="I4" t="n">
-        <v>-12.1</v>
-      </c>
-      <c r="J4" t="n">
-        <v>1</v>
-      </c>
       <c r="K4" t="n">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="L4" t="n">
-        <v>27</v>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Rotation lineup</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Futebol Clube do Porto</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>A. Bessa | C. Allen Williams | J. Guerreiro | T. Bropleh | V. Voytso</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="G5" t="n">
+        <v>94.5</v>
+      </c>
+      <c r="H5" t="n">
+        <v>87.7</v>
+      </c>
+      <c r="I5" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K5" t="n">
+        <v>22</v>
+      </c>
+      <c r="L5" t="n">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L4"/>
+  <autoFilter ref="A1:L5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1610,22 +1820,22 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F2" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="G2" t="n">
-        <v>59.8</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="H2" t="n">
-        <v>101.7</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>92.3</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="J2" t="n">
-        <v>9.4</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -1646,26 +1856,26 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>C. Dundao | T. Bropleh</t>
+          <t>C. Allen Williams | V. Voytso</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F3" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G3" t="n">
-        <v>54.2</v>
+        <v>56.4</v>
       </c>
       <c r="H3" t="n">
-        <v>98.90000000000001</v>
+        <v>102.9</v>
       </c>
       <c r="I3" t="n">
-        <v>87.09999999999999</v>
+        <v>84.5</v>
       </c>
       <c r="J3" t="n">
-        <v>11.8</v>
+        <v>18.5</v>
       </c>
     </row>
     <row r="4">
@@ -1686,26 +1896,26 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>C. Dundao | T. Bropleh</t>
+          <t>A. Bessa | C. Allen Williams</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F4" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G4" t="n">
-        <v>54.2</v>
+        <v>42.6</v>
       </c>
       <c r="H4" t="n">
-        <v>98.90000000000001</v>
+        <v>96.7</v>
       </c>
       <c r="I4" t="n">
-        <v>87.09999999999999</v>
+        <v>83.5</v>
       </c>
       <c r="J4" t="n">
-        <v>11.8</v>
+        <v>13.1</v>
       </c>
     </row>
     <row r="5">
@@ -1766,26 +1976,26 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>C. Allen Williams | C. Dundao | T. Bropleh</t>
+          <t>C. Allen Williams | T. Bropleh | V. Voytso</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F6" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G6" t="n">
-        <v>37</v>
+        <v>40.8</v>
       </c>
       <c r="H6" t="n">
-        <v>96.2</v>
+        <v>102.9</v>
       </c>
       <c r="I6" t="n">
-        <v>85.40000000000001</v>
+        <v>85.3</v>
       </c>
       <c r="J6" t="n">
-        <v>10.8</v>
+        <v>17.6</v>
       </c>
     </row>
     <row r="7">
@@ -1806,26 +2016,26 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>C. Allen Williams | C. Dundao | T. Bropleh</t>
+          <t>A. Bessa | C. Allen Williams | V. Voytso</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G7" t="n">
-        <v>37</v>
+        <v>38.9</v>
       </c>
       <c r="H7" t="n">
-        <v>96.2</v>
+        <v>100.8</v>
       </c>
       <c r="I7" t="n">
-        <v>85.40000000000001</v>
+        <v>83.3</v>
       </c>
       <c r="J7" t="n">
-        <v>10.8</v>
+        <v>17.5</v>
       </c>
     </row>
   </sheetData>
